--- a/EWS_output.xlsx
+++ b/EWS_output.xlsx
@@ -5994,10 +5994,10 @@
     <t>Compressed assessments</t>
   </si>
   <si>
-    <t>Hold graduate status -&gt; verify records &amp; re-assess sample -&gt; review with partner</t>
-  </si>
-  <si>
-    <t>Count as graduate -&gt; spot-check 10% -&gt; monitor next cycle</t>
+    <t>Hold graduate status → verify records &amp; re-assess sample → review with partner</t>
+  </si>
+  <si>
+    <t>Count as graduate → spot-check 10% → monitor next cycle</t>
   </si>
 </sst>
 </file>
